--- a/input/old/Metadata _Material Moving Average Price Change ( _20%)_SW_10_02_MAT_PRC_CHG.xlsx
+++ b/input/old/Metadata _Material Moving Average Price Change ( _20%)_SW_10_02_MAT_PRC_CHG.xlsx
@@ -422,7 +422,7 @@
         <v>Created on</v>
       </c>
       <c r="B6" t="str">
-        <v>28.11.2025 at 10:26 by ILIYAR</v>
+        <v>28.11.2025 at 10:26 by REDACTED</v>
       </c>
     </row>
     <row r="7">
